--- a/BOM/BillOfMaterials_v2.xlsx
+++ b/BOM/BillOfMaterials_v2.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2AC89B-D598-6D40-A157-ABABCDC4630C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD86198-E1C8-3B4F-8192-DBC1B78A10D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="2860" windowWidth="34400" windowHeight="23400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3560" yWindow="2860" windowWidth="34400" windowHeight="23400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -641,7 +641,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -669,10 +669,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -979,7 +975,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -1269,7 +1265,7 @@
         <v>118</v>
       </c>
       <c r="F13" s="2">
-        <f>C13*D13</f>
+        <f t="shared" ref="F13:F18" si="2">C13*D13</f>
         <v>38.97</v>
       </c>
       <c r="G13" s="2" t="s">
@@ -1281,7 +1277,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
-        <f>A13+1</f>
+        <f t="shared" ref="A14:A19" si="3">A13+1</f>
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1297,7 +1293,7 @@
         <v>124</v>
       </c>
       <c r="F14" s="2">
-        <f>C14*D14</f>
+        <f t="shared" si="2"/>
         <v>19.88</v>
       </c>
       <c r="G14" s="2" t="s">
@@ -1309,7 +1305,7 @@
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
-        <f>A14+1</f>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1325,7 +1321,7 @@
         <v>126</v>
       </c>
       <c r="F15" s="2">
-        <f>C15*D15</f>
+        <f t="shared" si="2"/>
         <v>6.89</v>
       </c>
       <c r="G15" s="2" t="s">
@@ -1337,7 +1333,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
-        <f>A15+1</f>
+        <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -1353,7 +1349,7 @@
         <v>128</v>
       </c>
       <c r="F16" s="2">
-        <f>C16*D16</f>
+        <f t="shared" si="2"/>
         <v>6.99</v>
       </c>
       <c r="G16" s="2" t="s">
@@ -1365,7 +1361,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
-        <f>A16+1</f>
+        <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
@@ -1381,7 +1377,7 @@
         <v>134</v>
       </c>
       <c r="F17" s="2">
-        <f>C17*D17</f>
+        <f t="shared" si="2"/>
         <v>8.99</v>
       </c>
       <c r="G17" s="2" t="s">
@@ -1393,7 +1389,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
-        <f>A17+1</f>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1409,7 +1405,7 @@
         <v>130</v>
       </c>
       <c r="F18" s="2">
-        <f>C18*D18</f>
+        <f t="shared" si="2"/>
         <v>7.49</v>
       </c>
       <c r="G18" s="2" t="s">
@@ -1421,7 +1417,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
-        <f>A18+1</f>
+        <f t="shared" si="3"/>
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
@@ -1447,13 +1443,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
+      <c r="B20" s="5"/>
       <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
@@ -1539,7 +1529,7 @@
         <v>67</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" ref="F25:F26" si="2">C25*D25</f>
+        <f t="shared" ref="F25:F26" si="4">C25*D25</f>
         <v>17.95</v>
       </c>
       <c r="G25" s="2" t="s">
@@ -1567,7 +1557,7 @@
         <v>71</v>
       </c>
       <c r="F26" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.95</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -1739,7 +1729,7 @@
         <v>50</v>
       </c>
       <c r="F36" s="2">
-        <f t="shared" ref="F36:F44" si="3">C36*D36</f>
+        <f t="shared" ref="F36:F44" si="5">C36*D36</f>
         <v>5.14</v>
       </c>
       <c r="G36" s="2" t="s">
@@ -1762,7 +1752,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9.65</v>
       </c>
       <c r="G37" s="2" t="s">
@@ -1787,7 +1777,7 @@
         <v>96</v>
       </c>
       <c r="F38" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9.65</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -1812,7 +1802,7 @@
         <v>84</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>9.99</v>
       </c>
       <c r="G39" s="2" t="s">
@@ -1837,7 +1827,7 @@
         <v>88</v>
       </c>
       <c r="F40" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15.99</v>
       </c>
       <c r="G40" s="2" t="s">
@@ -1862,7 +1852,7 @@
         <v>91</v>
       </c>
       <c r="F41" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>29.98</v>
       </c>
       <c r="G41" s="2" t="s">
@@ -1887,7 +1877,7 @@
         <v>104</v>
       </c>
       <c r="F42" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.2</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -1912,7 +1902,7 @@
         <v>103</v>
       </c>
       <c r="F43" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>6.41</v>
       </c>
       <c r="G43" s="2" t="s">
@@ -1937,7 +1927,7 @@
         <v>107</v>
       </c>
       <c r="F44" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3.69</v>
       </c>
       <c r="G44" s="2" t="s">
@@ -2175,175 +2165,26 @@
         <v>644.02999999999986</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
-      <c r="B60" s="20"/>
-      <c r="C60" s="20"/>
-      <c r="D60" s="20"/>
-      <c r="E60" s="20"/>
-      <c r="F60" s="20"/>
-      <c r="G60" s="20"/>
-      <c r="H60" s="20"/>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A61" s="20"/>
-      <c r="B61" s="20"/>
-      <c r="C61" s="20"/>
-      <c r="D61" s="20"/>
-      <c r="E61" s="20"/>
-      <c r="F61" s="20"/>
-      <c r="G61" s="20"/>
-      <c r="H61" s="20"/>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A62" s="20"/>
-      <c r="B62" s="20"/>
-      <c r="C62" s="20"/>
-      <c r="D62" s="20"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A63" s="20"/>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A64" s="20"/>
-      <c r="B64" s="20"/>
-      <c r="C64" s="20"/>
-      <c r="D64" s="20"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A65" s="20"/>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="H65" s="20"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A66" s="20"/>
-      <c r="B66" s="20"/>
-      <c r="C66" s="20"/>
-      <c r="D66" s="20"/>
-      <c r="E66" s="20"/>
-      <c r="F66" s="20"/>
-      <c r="G66" s="20"/>
-      <c r="H66" s="20"/>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
-      <c r="B67" s="20"/>
-      <c r="C67" s="20"/>
-      <c r="D67" s="20"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A68" s="20"/>
-      <c r="B68" s="20"/>
-      <c r="C68" s="20"/>
-      <c r="D68" s="20"/>
-      <c r="E68" s="20"/>
-      <c r="F68" s="20"/>
-      <c r="G68" s="20"/>
-      <c r="H68" s="20"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
-      <c r="B69" s="20"/>
-      <c r="C69" s="20"/>
-      <c r="D69" s="20"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
+    <row r="69" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H69" s="6"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A70" s="20"/>
-      <c r="B70" s="20"/>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="F70" s="20"/>
-      <c r="G70" s="20"/>
+    <row r="70" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H70" s="6"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A71" s="20"/>
-      <c r="B71" s="20"/>
-      <c r="C71" s="20"/>
-      <c r="D71" s="20"/>
-      <c r="E71" s="20"/>
-      <c r="F71" s="20"/>
-      <c r="G71" s="20"/>
+    <row r="71" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H71" s="6"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A72" s="20"/>
-      <c r="B72" s="20"/>
-      <c r="C72" s="20"/>
-      <c r="D72" s="20"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
+    <row r="72" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H72" s="6"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A73" s="20"/>
-      <c r="B73" s="20"/>
-      <c r="C73" s="20"/>
-      <c r="D73" s="20"/>
-      <c r="E73" s="20"/>
-      <c r="F73" s="20"/>
-      <c r="G73" s="20"/>
+    <row r="73" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H73" s="6"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A74" s="20"/>
-      <c r="B74" s="20"/>
-      <c r="C74" s="20"/>
-      <c r="D74" s="20"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
+    <row r="74" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H74" s="6"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A75" s="20"/>
-      <c r="B75" s="20"/>
-      <c r="C75" s="20"/>
-      <c r="D75" s="20"/>
-      <c r="E75" s="20"/>
-      <c r="F75" s="20"/>
-      <c r="G75" s="20"/>
+    <row r="75" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H75" s="6"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A76" s="20"/>
-      <c r="B76" s="20"/>
-      <c r="C76" s="20"/>
-      <c r="D76" s="20"/>
-      <c r="E76" s="20"/>
-      <c r="F76" s="20"/>
-      <c r="G76" s="20"/>
-      <c r="H76" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2528,7 +2369,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>136</v>
@@ -2584,7 +2425,7 @@
         <v>33</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>136</v>
@@ -2598,7 +2439,7 @@
         <v>34</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>136</v>
@@ -2640,7 +2481,7 @@
         <v>41</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>136</v>

--- a/BOM/BillOfMaterials_v2.xlsx
+++ b/BOM/BillOfMaterials_v2.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10613"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD86198-E1C8-3B4F-8192-DBC1B78A10D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7225A8DE-B7E1-D241-B4A9-E662CACDC0A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3560" yWindow="2860" windowWidth="34400" windowHeight="23400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="600" windowWidth="34400" windowHeight="20320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="166">
   <si>
     <t>Mechnical</t>
   </si>
@@ -226,24 +226,6 @@
     <t>1597-102010328-ND</t>
   </si>
   <si>
-    <t>https://www.sparkfun.com/products/14048</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/sparkfun-electronics/DEV-13736/5721426</t>
-  </si>
-  <si>
-    <t>1568-1231-ND</t>
-  </si>
-  <si>
-    <t>1568-1527-ND</t>
-  </si>
-  <si>
-    <t>K20 Teensy 3.2 Kinetis ARM® Cortex®-M4 MCU 32-Bit Embedded Evaluation Board (Discontinued)</t>
-  </si>
-  <si>
-    <t>SSD1306 OLED Display Teensy Platform Evaluation Expansion Board (Discontinued)</t>
-  </si>
-  <si>
     <t>1528-4540-ND</t>
   </si>
   <si>
@@ -518,6 +500,33 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/seeed-technology-co-ltd/102010672/26553862</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/5691/18627502</t>
+  </si>
+  <si>
+    <t>ESP32-S3 REVERSE TFT FEATHER</t>
+  </si>
+  <si>
+    <t>1528-5691-ND</t>
+  </si>
+  <si>
+    <t>1528-4538-ND</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4538/16584123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NAU7802 Analog to Digital Converter (ADC) Data Acquisition </t>
+  </si>
+  <si>
+    <t>1528-4399-ND</t>
+  </si>
+  <si>
+    <t>4 Position Cable Assembly Rectangular Socket to Socket 0.164' (50.00mm, 1.97")</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adafruit-industries-llc/4399/10824268</t>
   </si>
 </sst>
 </file>
@@ -549,7 +558,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -641,7 +649,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -665,10 +673,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -975,7 +987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
@@ -990,7 +1002,7 @@
         <v>10</v>
       </c>
       <c r="B1" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -1080,7 +1092,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2">
         <v>1</v>
@@ -1089,17 +1101,17 @@
         <v>11.99</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="0"/>
         <v>11.99</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -1108,7 +1120,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2">
         <v>1</v>
@@ -1117,45 +1129,45 @@
         <v>7.99</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>7.99</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="18">
+      <c r="A7" s="17">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C7" s="18">
-        <v>1</v>
-      </c>
-      <c r="D7" s="18">
+      <c r="B7" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="17">
+        <v>1</v>
+      </c>
+      <c r="D7" s="17">
         <v>6.99</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="F7" s="18">
+      <c r="E7" s="18" t="s">
+        <v>72</v>
+      </c>
+      <c r="F7" s="17">
         <f t="shared" si="0"/>
         <v>6.99</v>
       </c>
-      <c r="G7" s="18" t="s">
-        <v>75</v>
+      <c r="G7" s="17" t="s">
+        <v>69</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
@@ -1164,7 +1176,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
@@ -1173,17 +1185,17 @@
         <v>31.99</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>31.99</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
@@ -1192,7 +1204,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2">
         <v>1</v>
@@ -1201,17 +1213,17 @@
         <v>89.99</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>89.99</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -1253,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
@@ -1262,17 +1274,17 @@
         <v>12.99</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" ref="F13:F18" si="2">C13*D13</f>
         <v>38.97</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -1281,7 +1293,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2">
         <v>1</v>
@@ -1290,17 +1302,17 @@
         <v>19.88</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="2"/>
         <v>19.88</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -1318,17 +1330,17 @@
         <v>6.89</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="2"/>
         <v>6.89</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
@@ -1337,7 +1349,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C16" s="2">
         <v>1</v>
@@ -1346,17 +1358,17 @@
         <v>6.99</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="2"/>
         <v>6.99</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
@@ -1365,7 +1377,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C17" s="2">
         <v>1</v>
@@ -1374,17 +1386,17 @@
         <v>8.99</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" si="2"/>
         <v>8.99</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
@@ -1393,7 +1405,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C18" s="2">
         <v>1</v>
@@ -1402,17 +1414,17 @@
         <v>7.49</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" si="2"/>
         <v>7.49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
@@ -1421,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C19" s="2">
         <v>1</v>
@@ -1430,7 +1442,7 @@
         <v>10.4</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="F19" s="2">
         <v>10.4</v>
@@ -1439,7 +1451,7 @@
         <v>52</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
@@ -1485,39 +1497,39 @@
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24">
-        <v>1</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>69</v>
+      <c r="A24" s="2">
+        <v>1</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>158</v>
       </c>
       <c r="C24" s="2">
         <v>1</v>
       </c>
       <c r="D24" s="2">
-        <v>21.88</v>
+        <v>24.95</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>68</v>
+        <v>159</v>
       </c>
       <c r="F24" s="2">
         <f>C24*D24</f>
-        <v>21.88</v>
+        <v>24.95</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A25">
+      <c r="A25" s="2">
         <f>A24+1</f>
         <v>2</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>70</v>
+      <c r="B25" s="20" t="s">
+        <v>162</v>
       </c>
       <c r="C25" s="2">
         <v>1</v>
@@ -1526,25 +1538,25 @@
         <v>17.95</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>160</v>
       </c>
       <c r="F25" s="2">
-        <f t="shared" ref="F25:F26" si="4">C25*D25</f>
+        <f t="shared" ref="F25:F27" si="4">C25*D25</f>
         <v>17.95</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>52</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26">
+      <c r="A26" s="2">
         <f>A25+1</f>
         <v>3</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C26" s="2">
@@ -1554,7 +1566,7 @@
         <v>3.95</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="4"/>
@@ -1567,205 +1579,210 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B27" s="5"/>
-      <c r="H27" s="6"/>
+    <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <f>A26+1</f>
+        <v>4</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C27" s="19">
+        <v>1</v>
+      </c>
+      <c r="D27" s="19">
+        <v>0.95</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="4"/>
+        <v>0.95</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A28" s="11" t="s">
+      <c r="B28" s="5"/>
+      <c r="H28" s="6"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B28" s="11" t="s">
+      <c r="B29" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" s="13" t="s">
+      <c r="C29" s="11"/>
+      <c r="D29" s="11"/>
+      <c r="E29" s="11"/>
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+      <c r="H29" s="11"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A30" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D30" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="E29" s="13" t="s">
+      <c r="E30" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F30" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G30" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" s="14">
-        <v>1</v>
-      </c>
-      <c r="B30" s="15" t="s">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" s="14">
+        <v>1</v>
+      </c>
+      <c r="B31" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="15">
-        <v>1</v>
-      </c>
-      <c r="D30" s="15">
+      <c r="C31" s="15">
+        <v>1</v>
+      </c>
+      <c r="D31" s="15">
         <v>5.4</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E31" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="15">
-        <f>C30*D30</f>
+      <c r="F31" s="15">
+        <f>C31*D31</f>
         <v>5.4</v>
       </c>
-      <c r="G30" s="2" t="s">
+      <c r="G31" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H30" s="16" t="s">
+      <c r="H31" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="2">
-        <f>A30+1</f>
+    <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <f>A31+1</f>
         <v>2</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="2">
-        <v>1</v>
-      </c>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2" t="s">
+      <c r="B32" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="2">
+        <v>1</v>
+      </c>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="3"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="3"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
         <v>0</v>
       </c>
-      <c r="B33" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A34" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C35" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D35" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E35" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
+      <c r="F35" s="2"/>
+      <c r="G35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="2" t="s">
+      <c r="H35" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="2"/>
-      <c r="B35" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C35" s="2">
-        <v>7</v>
-      </c>
-      <c r="D35" s="2">
-        <v>21.13</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="2">
-        <f>C35*D35</f>
-        <v>147.91</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="2"/>
       <c r="B36" s="2" t="s">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="C36" s="2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D36" s="2">
-        <v>5.14</v>
+        <v>21.13</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F36" s="2">
-        <f t="shared" ref="F36:F44" si="5">C36*D36</f>
-        <v>5.14</v>
+        <f>C36*D36</f>
+        <v>147.91</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="H36" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="2"/>
-      <c r="B37" s="4" t="s">
-        <v>95</v>
+      <c r="B37" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="C37" s="2">
         <v>1</v>
       </c>
       <c r="D37" s="2">
-        <v>9.65</v>
-      </c>
-      <c r="E37" s="2"/>
+        <v>5.14</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="F37" s="2">
-        <f t="shared" si="5"/>
-        <v>9.65</v>
+        <f t="shared" ref="F37:F45" si="5">C37*D37</f>
+        <v>5.14</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C38" s="2">
         <v>1</v>
@@ -1773,9 +1790,7 @@
       <c r="D38" s="2">
         <v>9.65</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>96</v>
-      </c>
+      <c r="E38" s="2"/>
       <c r="F38" s="2">
         <f t="shared" si="5"/>
         <v>9.65</v>
@@ -1784,389 +1799,411 @@
         <v>9</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2"/>
       <c r="B39" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C39" s="2">
         <v>1</v>
       </c>
       <c r="D39" s="2">
-        <v>9.99</v>
+        <v>9.65</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="5"/>
+        <v>9.65</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="2"/>
+      <c r="B40" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="2">
+        <v>1</v>
+      </c>
+      <c r="D40" s="2">
         <v>9.99</v>
       </c>
-      <c r="G39" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="2">
-        <v>1</v>
-      </c>
-      <c r="D40" s="2">
-        <v>15.99</v>
-      </c>
       <c r="E40" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" si="5"/>
+        <v>9.99</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="2">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2">
         <v>15.99</v>
       </c>
-      <c r="G40" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="2"/>
-      <c r="B41" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="C41" s="2">
-        <v>2</v>
-      </c>
-      <c r="D41" s="2">
-        <v>14.99</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" si="5"/>
-        <v>29.98</v>
+        <v>15.99</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="4" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="C42" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D42" s="2">
-        <v>6.2</v>
+        <v>14.99</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="5"/>
-        <v>6.2</v>
+        <v>29.98</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2"/>
       <c r="B43" s="4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="C43" s="2">
         <v>1</v>
       </c>
       <c r="D43" s="2">
-        <v>6.41</v>
+        <v>6.2</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F43" s="2">
         <f t="shared" si="5"/>
-        <v>6.41</v>
+        <v>6.2</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2"/>
       <c r="B44" s="4" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C44" s="2">
         <v>1</v>
       </c>
       <c r="D44" s="2">
-        <v>3.69</v>
+        <v>6.41</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" si="5"/>
-        <v>3.69</v>
+        <v>6.41</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>9</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="B45" s="5"/>
-      <c r="H45" s="1"/>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="2"/>
+      <c r="B45" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C45" s="2">
+        <v>1</v>
+      </c>
+      <c r="D45" s="2">
+        <v>3.69</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F45" s="2">
+        <f t="shared" si="5"/>
+        <v>3.69</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
+      <c r="B46" s="5"/>
+      <c r="H46" s="1"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
         <v>0</v>
       </c>
-      <c r="B46" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="C48" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D48" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E48" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
+      <c r="F48" s="2"/>
+      <c r="G48" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H47" s="2" t="s">
+      <c r="H48" s="2" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C48" s="2">
-        <v>1</v>
-      </c>
-      <c r="D48" s="2">
-        <v>9.49</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F48" s="2">
-        <f>C48*D48</f>
-        <v>9.49</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="2"/>
       <c r="B49" s="2" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C49" s="2">
         <v>1</v>
       </c>
       <c r="D49" s="2">
-        <v>6.69</v>
+        <v>9.49</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="F49" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="F49" s="2">
+        <f>C49*D49</f>
+        <v>9.49</v>
+      </c>
       <c r="G49" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="2"/>
       <c r="B50" s="2" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C50" s="2">
         <v>1</v>
       </c>
       <c r="D50" s="2">
-        <v>17.09</v>
+        <v>6.69</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="F50" s="2"/>
       <c r="G50" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="2"/>
       <c r="B51" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="C51" s="2">
         <v>1</v>
       </c>
       <c r="D51" s="2">
-        <v>9.99</v>
+        <v>17.09</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="G51" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="H51" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="2"/>
       <c r="B52" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C52" s="2">
         <v>1</v>
       </c>
       <c r="D52" s="2">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F52" s="2"/>
       <c r="G52" s="2"/>
       <c r="H52" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="2"/>
       <c r="B53" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C53" s="2">
         <v>1</v>
       </c>
       <c r="D53" s="2">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="2"/>
       <c r="B54" s="2" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="C54" s="2">
         <v>1</v>
       </c>
       <c r="D54" s="2">
-        <v>12.29</v>
+        <v>8.99</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F54" s="2">
-        <f>C54*D54</f>
-        <v>12.29</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>75</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
       <c r="H54" s="3" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="2"/>
       <c r="B55" s="2" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="C55" s="2">
         <v>1</v>
       </c>
-      <c r="D55" s="2"/>
+      <c r="D55" s="2">
+        <v>12.29</v>
+      </c>
       <c r="E55" s="2" t="s">
-        <v>18</v>
+        <v>103</v>
       </c>
       <c r="F55" s="2">
         <f>C55*D55</f>
-        <v>0</v>
-      </c>
-      <c r="G55" s="2"/>
-      <c r="H55" s="3"/>
+        <v>12.29</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="2"/>
+      <c r="B56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C56" s="2">
+        <v>1</v>
+      </c>
       <c r="D56" s="2"/>
-      <c r="E56" s="2"/>
-      <c r="F56" s="2"/>
+      <c r="E56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="2">
+        <f>C56*D56</f>
+        <v>0</v>
+      </c>
       <c r="G56" s="2"/>
       <c r="H56" s="3"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="E59" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="E60" t="s">
         <v>13</v>
       </c>
-      <c r="F59">
-        <f>SUM(F3:F57)</f>
-        <v>644.02999999999986</v>
-      </c>
-    </row>
-    <row r="69" spans="8:8" x14ac:dyDescent="0.2">
-      <c r="H69" s="6"/>
+      <c r="F60">
+        <f>SUM(F3:F58)</f>
+        <v>648.04999999999984</v>
+      </c>
     </row>
     <row r="70" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H70" s="6"/>
@@ -2186,36 +2223,39 @@
     <row r="75" spans="8:8" x14ac:dyDescent="0.2">
       <c r="H75" s="6"/>
     </row>
+    <row r="76" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H76" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H36" r:id="rId1" xr:uid="{835118DB-F794-7941-BEB3-A50BB95D1701}"/>
+    <hyperlink ref="H37" r:id="rId1" xr:uid="{835118DB-F794-7941-BEB3-A50BB95D1701}"/>
     <hyperlink ref="H26" r:id="rId2" xr:uid="{7A6F4A79-4DA6-564D-B998-55552CEB6B08}"/>
     <hyperlink ref="H4" r:id="rId3" xr:uid="{FAAD29BA-34B7-1D41-9E69-586E54E14FC8}"/>
     <hyperlink ref="H3" r:id="rId4" xr:uid="{C59E9856-CCEE-1245-8754-8A2367785095}"/>
-    <hyperlink ref="H30" r:id="rId5" xr:uid="{536D0B01-0066-BB40-9024-F8F75FC760C3}"/>
+    <hyperlink ref="H31" r:id="rId5" xr:uid="{536D0B01-0066-BB40-9024-F8F75FC760C3}"/>
     <hyperlink ref="H24" r:id="rId6" xr:uid="{CD8889CA-470A-5B45-A584-53E59D730888}"/>
     <hyperlink ref="H25" r:id="rId7" xr:uid="{3332DC8B-1836-AA43-B12D-47AF1A9ADB45}"/>
     <hyperlink ref="H5" r:id="rId8" xr:uid="{9CC180F9-0823-CD48-8BEC-34FFF6BFBE2A}"/>
     <hyperlink ref="H7" r:id="rId9" xr:uid="{6F1804AA-010E-BA47-BB2C-4DB9787A096B}"/>
     <hyperlink ref="H6" r:id="rId10" xr:uid="{605067D0-36AC-FC4C-BF2C-93238E3DE100}"/>
-    <hyperlink ref="H39" r:id="rId11" xr:uid="{1DFBFFDB-35F2-8840-8291-DFFE5BCD9751}"/>
-    <hyperlink ref="H40" r:id="rId12" xr:uid="{FDBDEC55-434F-054E-9041-3DA3E9C46C88}"/>
-    <hyperlink ref="H41" r:id="rId13" xr:uid="{AF1CE6D5-3B0B-E74D-9187-069B5E71026E}"/>
-    <hyperlink ref="H35" r:id="rId14" xr:uid="{16BF5847-7290-8548-8454-1DE58EABE1CA}"/>
-    <hyperlink ref="H37" r:id="rId15" xr:uid="{D5F1188A-1192-E641-9888-AB87C35F378E}"/>
-    <hyperlink ref="H38" r:id="rId16" xr:uid="{73C42B54-A324-1E4D-94C1-055C0436FA47}"/>
-    <hyperlink ref="H42" r:id="rId17" xr:uid="{3BB8C3DC-0C02-E546-B957-BD7A12CE07D9}"/>
-    <hyperlink ref="H43" r:id="rId18" xr:uid="{7D4E5FE4-4319-244A-9E63-79D89E552C18}"/>
-    <hyperlink ref="H44" r:id="rId19" xr:uid="{D0C117C6-81E6-1E4D-A199-72530F46095D}"/>
+    <hyperlink ref="H40" r:id="rId11" xr:uid="{1DFBFFDB-35F2-8840-8291-DFFE5BCD9751}"/>
+    <hyperlink ref="H41" r:id="rId12" xr:uid="{FDBDEC55-434F-054E-9041-3DA3E9C46C88}"/>
+    <hyperlink ref="H42" r:id="rId13" xr:uid="{AF1CE6D5-3B0B-E74D-9187-069B5E71026E}"/>
+    <hyperlink ref="H36" r:id="rId14" xr:uid="{16BF5847-7290-8548-8454-1DE58EABE1CA}"/>
+    <hyperlink ref="H38" r:id="rId15" xr:uid="{D5F1188A-1192-E641-9888-AB87C35F378E}"/>
+    <hyperlink ref="H39" r:id="rId16" xr:uid="{73C42B54-A324-1E4D-94C1-055C0436FA47}"/>
+    <hyperlink ref="H43" r:id="rId17" xr:uid="{3BB8C3DC-0C02-E546-B957-BD7A12CE07D9}"/>
+    <hyperlink ref="H44" r:id="rId18" xr:uid="{7D4E5FE4-4319-244A-9E63-79D89E552C18}"/>
+    <hyperlink ref="H45" r:id="rId19" xr:uid="{D0C117C6-81E6-1E4D-A199-72530F46095D}"/>
     <hyperlink ref="H8" r:id="rId20" xr:uid="{97840DF5-C32F-D446-B016-C507F24F3DDF}"/>
     <hyperlink ref="H9" r:id="rId21" xr:uid="{5932D35D-59E1-1E45-B840-1B4006055868}"/>
-    <hyperlink ref="H54" r:id="rId22" xr:uid="{CE4A89F6-D0D7-CA45-8A54-DEBC31B7C4A6}"/>
-    <hyperlink ref="H48" r:id="rId23" xr:uid="{1F00893A-02C0-5C41-A1EB-739DA7F3E6AC}"/>
-    <hyperlink ref="H49" r:id="rId24" xr:uid="{96220297-898D-AA4C-88C0-BFC7CE9738A4}"/>
-    <hyperlink ref="H50" r:id="rId25" xr:uid="{98348940-B3B0-1D46-92B6-B624F4E84CB0}"/>
-    <hyperlink ref="H51" r:id="rId26" xr:uid="{3CE4FDAE-B1F4-0C40-AC9D-29B27419D6B6}"/>
-    <hyperlink ref="H52" r:id="rId27" xr:uid="{E207FFE9-E655-0B4A-B921-02CA4D2548DA}"/>
-    <hyperlink ref="H53" r:id="rId28" xr:uid="{4DBE40C8-A220-A447-A0DE-D19C8208AE80}"/>
+    <hyperlink ref="H55" r:id="rId22" xr:uid="{CE4A89F6-D0D7-CA45-8A54-DEBC31B7C4A6}"/>
+    <hyperlink ref="H49" r:id="rId23" xr:uid="{1F00893A-02C0-5C41-A1EB-739DA7F3E6AC}"/>
+    <hyperlink ref="H50" r:id="rId24" xr:uid="{96220297-898D-AA4C-88C0-BFC7CE9738A4}"/>
+    <hyperlink ref="H51" r:id="rId25" xr:uid="{98348940-B3B0-1D46-92B6-B624F4E84CB0}"/>
+    <hyperlink ref="H52" r:id="rId26" xr:uid="{3CE4FDAE-B1F4-0C40-AC9D-29B27419D6B6}"/>
+    <hyperlink ref="H53" r:id="rId27" xr:uid="{E207FFE9-E655-0B4A-B921-02CA4D2548DA}"/>
+    <hyperlink ref="H54" r:id="rId28" xr:uid="{4DBE40C8-A220-A447-A0DE-D19C8208AE80}"/>
     <hyperlink ref="H13" r:id="rId29" xr:uid="{58D72F74-03CA-0740-9CB2-F8D2FB034482}"/>
     <hyperlink ref="H14" r:id="rId30" xr:uid="{9E9A7A98-0859-664D-9985-19189717E51C}"/>
     <hyperlink ref="H18" r:id="rId31" xr:uid="{A909D9E6-F527-3244-8304-702826B01470}"/>
@@ -2246,7 +2286,7 @@
         <v>45</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="D1" t="s">
         <v>21</v>
@@ -2260,7 +2300,7 @@
         <v>46</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2274,7 +2314,7 @@
         <v>46</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2285,10 +2325,10 @@
         <v>23</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2302,7 +2342,7 @@
         <v>46</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2316,7 +2356,7 @@
         <v>46</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2327,10 +2367,10 @@
         <v>26</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2344,7 +2384,7 @@
         <v>46</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2358,7 +2398,7 @@
         <v>46</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2372,7 +2412,7 @@
         <v>47</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2386,7 +2426,7 @@
         <v>46</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2400,7 +2440,7 @@
         <v>46</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2414,7 +2454,7 @@
         <v>47</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2428,7 +2468,7 @@
         <v>47</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2442,7 +2482,7 @@
         <v>46</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2456,7 +2496,7 @@
         <v>46</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -2470,7 +2510,7 @@
         <v>46</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2484,7 +2524,7 @@
         <v>47</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D18">
         <v>1</v>
@@ -2498,7 +2538,7 @@
         <v>46</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -2512,7 +2552,7 @@
         <v>46</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -2526,7 +2566,7 @@
         <v>47</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -2540,7 +2580,7 @@
         <v>46</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D22">
         <v>1</v>
@@ -2548,13 +2588,13 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -2562,13 +2602,13 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>46</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -2588,7 +2628,7 @@
         <v>47</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -2602,7 +2642,7 @@
         <v>47</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -2616,7 +2656,7 @@
         <v>47</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D29">
         <v>2</v>
